--- a/data/industry/CFM/eMMC.xlsx
+++ b/data/industry/CFM/eMMC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93847322-AEE4-4BA6-A414-96058A35622E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5227D2BD-AECC-4495-B090-90571398F2A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1086,7 +1086,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -1099,6 +1099,121 @@
       </c>
       <c r="G28" s="10">
         <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>14.6</v>
+      </c>
+      <c r="F29" s="10">
+        <v>15.5</v>
+      </c>
+      <c r="G29" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>14.6</v>
+      </c>
+      <c r="F30" s="10">
+        <v>15.5</v>
+      </c>
+      <c r="G30" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>14.6</v>
+      </c>
+      <c r="F31" s="10">
+        <v>15.5</v>
+      </c>
+      <c r="G31" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F32" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="G32" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F33" s="10">
+        <v>20.5</v>
+      </c>
+      <c r="G33" s="10">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1109,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3458BA-C690-425E-897C-D26F43A0AC55}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1750,7 +1865,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -1763,6 +1878,121 @@
       </c>
       <c r="G28" s="10">
         <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>15.8</v>
+      </c>
+      <c r="F29" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="G29" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>15.8</v>
+      </c>
+      <c r="F30" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="G30" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>15.8</v>
+      </c>
+      <c r="F31" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="G31" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>18.8</v>
+      </c>
+      <c r="F32" s="10">
+        <v>20.3</v>
+      </c>
+      <c r="G32" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>20.8</v>
+      </c>
+      <c r="F33" s="10">
+        <v>22.3</v>
+      </c>
+      <c r="G33" s="10">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1773,7 +2003,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4C3C62-4D14-4156-9017-943BF365E5C9}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -2414,7 +2644,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -2427,6 +2657,121 @@
       </c>
       <c r="G28" s="10">
         <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F29" s="10">
+        <v>18.3</v>
+      </c>
+      <c r="G29" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F30" s="10">
+        <v>18.3</v>
+      </c>
+      <c r="G30" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F31" s="10">
+        <v>18.3</v>
+      </c>
+      <c r="G31" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>21.6</v>
+      </c>
+      <c r="F32" s="10">
+        <v>23.3</v>
+      </c>
+      <c r="G32" s="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="F33" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="G33" s="10">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2437,7 +2782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB386A95-5195-4084-9FB9-971921256B62}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -3078,7 +3423,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -3091,6 +3436,121 @@
       </c>
       <c r="G28" s="10">
         <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="F29" s="10">
+        <v>20</v>
+      </c>
+      <c r="G29" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="F30" s="10">
+        <v>20</v>
+      </c>
+      <c r="G30" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="F31" s="10">
+        <v>20</v>
+      </c>
+      <c r="G31" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>22.5</v>
+      </c>
+      <c r="F32" s="10">
+        <v>24</v>
+      </c>
+      <c r="G32" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>24.5</v>
+      </c>
+      <c r="F33" s="10">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3101,7 +3561,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29CFE0E-1939-4F13-BC18-8B4E3159446B}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -3742,7 +4202,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -3755,6 +4215,121 @@
       </c>
       <c r="G28" s="10">
         <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>27.4</v>
+      </c>
+      <c r="F29" s="10">
+        <v>30.5</v>
+      </c>
+      <c r="G29" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>27.4</v>
+      </c>
+      <c r="F30" s="10">
+        <v>30.5</v>
+      </c>
+      <c r="G30" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>27.4</v>
+      </c>
+      <c r="F31" s="10">
+        <v>30.5</v>
+      </c>
+      <c r="G31" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="F32" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="G32" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="F33" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="G33" s="10">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3765,7 +4340,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEFF7D63-8706-4CE6-8EDE-86A6F3873A2B}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -4406,7 +4981,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -4419,6 +4994,121 @@
       </c>
       <c r="G28" s="10">
         <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>48.1</v>
+      </c>
+      <c r="F29" s="10">
+        <v>52.5</v>
+      </c>
+      <c r="G29" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>48.1</v>
+      </c>
+      <c r="F30" s="10">
+        <v>52.5</v>
+      </c>
+      <c r="G30" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>48.1</v>
+      </c>
+      <c r="F31" s="10">
+        <v>52.5</v>
+      </c>
+      <c r="G31" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="F32" s="10">
+        <v>60.5</v>
+      </c>
+      <c r="G32" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="F33" s="10">
+        <v>60.5</v>
+      </c>
+      <c r="G33" s="10">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/eMMC.xlsx
+++ b/data/industry/CFM/eMMC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497898FA-F145-4EA3-A0DD-C6AA3FD0ECA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1BC210-5901-4EEB-A58B-9ACD7C682B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -72,23 +72,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -101,7 +101,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -132,38 +132,38 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -445,19 +445,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -503,7 +503,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -549,7 +549,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -572,7 +572,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -595,7 +595,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -618,7 +618,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -641,7 +641,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -664,7 +664,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -687,7 +687,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -710,7 +710,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -733,7 +733,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -756,7 +756,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -779,7 +779,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -802,7 +802,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -825,7 +825,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -848,7 +848,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -871,7 +871,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -894,7 +894,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -917,7 +917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -940,7 +940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -963,7 +963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -1351,6 +1351,144 @@
         <v>20.5</v>
       </c>
       <c r="G39" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F40" s="10">
+        <v>20.5</v>
+      </c>
+      <c r="G40" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F41" s="10">
+        <v>20.5</v>
+      </c>
+      <c r="G41" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F42" s="10">
+        <v>20.5</v>
+      </c>
+      <c r="G42" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F43" s="10">
+        <v>20.5</v>
+      </c>
+      <c r="G43" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F44" s="10">
+        <v>20.5</v>
+      </c>
+      <c r="G44" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F45" s="10">
+        <v>20.5</v>
+      </c>
+      <c r="G45" s="10">
         <v>20</v>
       </c>
     </row>
@@ -1362,19 +1500,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3458BA-C690-425E-897C-D26F43A0AC55}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1397,7 +1535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -1420,7 +1558,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -1443,7 +1581,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -1466,7 +1604,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -1489,7 +1627,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -1512,7 +1650,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -1535,7 +1673,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -1558,7 +1696,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -1581,7 +1719,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -1604,7 +1742,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -1627,7 +1765,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -1650,7 +1788,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -1673,7 +1811,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -1696,7 +1834,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -1719,7 +1857,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -1742,7 +1880,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -1765,7 +1903,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -1788,7 +1926,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -1811,7 +1949,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -1834,7 +1972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -1857,7 +1995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -1880,7 +2018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -1903,7 +2041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1926,7 +2064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1949,7 +2087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1972,7 +2110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -1995,7 +2133,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -2018,7 +2156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2041,7 +2179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2064,7 +2202,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -2087,7 +2225,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -2110,7 +2248,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -2133,7 +2271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -2156,7 +2294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -2179,7 +2317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -2202,7 +2340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -2225,7 +2363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -2248,7 +2386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -2268,6 +2406,144 @@
         <v>22.3</v>
       </c>
       <c r="G39" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>20.8</v>
+      </c>
+      <c r="F40" s="10">
+        <v>22.3</v>
+      </c>
+      <c r="G40" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>20.8</v>
+      </c>
+      <c r="F41" s="10">
+        <v>22.3</v>
+      </c>
+      <c r="G41" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>20.8</v>
+      </c>
+      <c r="F42" s="10">
+        <v>22.3</v>
+      </c>
+      <c r="G42" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>20.8</v>
+      </c>
+      <c r="F43" s="10">
+        <v>22.3</v>
+      </c>
+      <c r="G43" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>20.8</v>
+      </c>
+      <c r="F44" s="10">
+        <v>22.3</v>
+      </c>
+      <c r="G44" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>20.8</v>
+      </c>
+      <c r="F45" s="10">
+        <v>22.3</v>
+      </c>
+      <c r="G45" s="10">
         <v>21</v>
       </c>
     </row>
@@ -2279,19 +2555,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4C3C62-4D14-4156-9017-943BF365E5C9}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2314,7 +2590,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -2337,7 +2613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -2360,7 +2636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -2383,7 +2659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -2406,7 +2682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -2429,7 +2705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -2452,7 +2728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -2475,7 +2751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -2498,7 +2774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -2521,7 +2797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -2544,7 +2820,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -2567,7 +2843,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -2590,7 +2866,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -2613,7 +2889,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -2636,7 +2912,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -2659,7 +2935,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -2682,7 +2958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -2705,7 +2981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -2728,7 +3004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -2751,7 +3027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -2774,7 +3050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -2797,7 +3073,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -2820,7 +3096,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -2843,7 +3119,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -2866,7 +3142,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -2889,7 +3165,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -2912,7 +3188,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -2935,7 +3211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2958,7 +3234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2981,7 +3257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -3004,7 +3280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -3027,7 +3303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -3050,7 +3326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -3073,7 +3349,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -3096,7 +3372,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -3119,7 +3395,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -3142,7 +3418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -3165,7 +3441,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -3185,6 +3461,144 @@
         <v>24.3</v>
       </c>
       <c r="G39" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="F40" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="G40" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="F41" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="G41" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="F42" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="G42" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="F43" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="G43" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="F44" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="G44" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="F45" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="G45" s="10">
         <v>23</v>
       </c>
     </row>
@@ -3196,19 +3610,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB386A95-5195-4084-9FB9-971921256B62}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3231,7 +3645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -3254,7 +3668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -3277,7 +3691,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -3300,7 +3714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -3323,7 +3737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -3346,7 +3760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -3369,7 +3783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -3392,7 +3806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -3415,7 +3829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -3438,7 +3852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -3461,7 +3875,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -3484,7 +3898,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -3507,7 +3921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -3530,7 +3944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -3553,7 +3967,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -3576,7 +3990,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -3599,7 +4013,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -3622,7 +4036,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -3645,7 +4059,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -3668,7 +4082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -3691,7 +4105,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -3714,7 +4128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -3737,7 +4151,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -3760,7 +4174,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -3783,7 +4197,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -3806,7 +4220,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -3829,7 +4243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -3852,7 +4266,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -3875,7 +4289,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -3898,7 +4312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -3921,7 +4335,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -3944,7 +4358,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -3967,7 +4381,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -3990,7 +4404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -4013,7 +4427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -4036,7 +4450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -4059,7 +4473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -4082,7 +4496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -4102,6 +4516,144 @@
         <v>26</v>
       </c>
       <c r="G39" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>24.5</v>
+      </c>
+      <c r="F40" s="10">
+        <v>26</v>
+      </c>
+      <c r="G40" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>24.5</v>
+      </c>
+      <c r="F41" s="10">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>24.5</v>
+      </c>
+      <c r="F42" s="10">
+        <v>26</v>
+      </c>
+      <c r="G42" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>24.5</v>
+      </c>
+      <c r="F43" s="10">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>24.5</v>
+      </c>
+      <c r="F44" s="10">
+        <v>26</v>
+      </c>
+      <c r="G44" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>24.5</v>
+      </c>
+      <c r="F45" s="10">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10">
         <v>25</v>
       </c>
     </row>
@@ -4113,19 +4665,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29CFE0E-1939-4F13-BC18-8B4E3159446B}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4148,7 +4700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -4171,7 +4723,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -4194,7 +4746,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -4217,7 +4769,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -4240,7 +4792,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -4263,7 +4815,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -4286,7 +4838,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -4309,7 +4861,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -4332,7 +4884,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -4355,7 +4907,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -4378,7 +4930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -4401,7 +4953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -4424,7 +4976,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -4447,7 +4999,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -4470,7 +5022,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -4493,7 +5045,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -4516,7 +5068,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -4539,7 +5091,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -4562,7 +5114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -4585,7 +5137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -4608,7 +5160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -4631,7 +5183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -4654,7 +5206,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -4677,7 +5229,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -4700,7 +5252,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -4723,7 +5275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -4746,7 +5298,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -4769,7 +5321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -4792,7 +5344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -4815,7 +5367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -4838,7 +5390,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -4861,7 +5413,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -4884,7 +5436,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -4907,7 +5459,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -4930,7 +5482,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -4953,7 +5505,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -4976,7 +5528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -4999,7 +5551,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -5019,6 +5571,144 @@
         <v>33.5</v>
       </c>
       <c r="G39" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="F40" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="G40" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="F41" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="G41" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="F42" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="G42" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="F43" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="G43" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="F44" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="G44" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>30.4</v>
+      </c>
+      <c r="F45" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="G45" s="10">
         <v>31</v>
       </c>
     </row>
@@ -5030,19 +5720,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEFF7D63-8706-4CE6-8EDE-86A6F3873A2B}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5065,7 +5755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -5088,7 +5778,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -5111,7 +5801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -5134,7 +5824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -5157,7 +5847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -5180,7 +5870,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -5203,7 +5893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -5226,7 +5916,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -5249,7 +5939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -5272,7 +5962,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -5295,7 +5985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -5318,7 +6008,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -5341,7 +6031,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -5364,7 +6054,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -5387,7 +6077,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -5410,7 +6100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -5433,7 +6123,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -5456,7 +6146,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -5479,7 +6169,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -5502,7 +6192,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -5525,7 +6215,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -5548,7 +6238,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -5571,7 +6261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -5594,7 +6284,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -5617,7 +6307,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -5640,7 +6330,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -5663,7 +6353,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -5686,7 +6376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -5709,7 +6399,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -5732,7 +6422,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -5755,7 +6445,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -5778,7 +6468,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -5801,7 +6491,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -5824,7 +6514,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -5847,7 +6537,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -5870,7 +6560,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -5893,7 +6583,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -5916,7 +6606,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -5936,6 +6626,144 @@
         <v>60.5</v>
       </c>
       <c r="G39" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="F40" s="10">
+        <v>60.5</v>
+      </c>
+      <c r="G40" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="F41" s="10">
+        <v>60.5</v>
+      </c>
+      <c r="G41" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="F42" s="10">
+        <v>60.5</v>
+      </c>
+      <c r="G42" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="F43" s="10">
+        <v>60.5</v>
+      </c>
+      <c r="G43" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="F44" s="10">
+        <v>60.5</v>
+      </c>
+      <c r="G44" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>56.1</v>
+      </c>
+      <c r="F45" s="10">
+        <v>60.5</v>
+      </c>
+      <c r="G45" s="10">
         <v>58</v>
       </c>
     </row>
